--- a/New_Fuzzy_Rules.xlsx
+++ b/New_Fuzzy_Rules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\PMSM-control-using-FOC-and-tuned-PI-controller-using-Simulink\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A7EC34-67A1-4237-B1B7-4746F497BF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEF8DF5-4902-488C-9F5A-F6FE5EA606E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9BFB8E41-E711-40F0-ADCE-7C5B88288570}"/>
   </bookViews>
@@ -134,10 +134,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -145,6 +143,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,425 +480,425 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="J1" s="6" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="4" t="s">
+      <c r="K3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="2" t="s">
+      <c r="A4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q4" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>6</v>
+      <c r="A5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="10" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="2" t="s">
+      <c r="A6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>0</v>
+      <c r="A7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>1</v>
+      <c r="A8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>6</v>
+      <c r="A9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="10" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>3</v>
+      <c r="A10" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="10" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
